--- a/similar_indicators.xlsx
+++ b/similar_indicators.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanis\Documents\scripts\indicators_public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLU-SU\Documents\GitHub\indicators_public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FE50125-B5CA-417B-8222-5483EAC2A294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52592A7B-644E-4765-8394-C82DA839EB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Similar indicators" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2990" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2990" uniqueCount="941">
   <si>
     <t>Group</t>
   </si>
@@ -1246,9 +1246,6 @@
     <t>GBF, GEO</t>
   </si>
   <si>
-    <t>Concept vs composite index</t>
-  </si>
-  <si>
     <t>agrobiodiversity index</t>
   </si>
   <si>
@@ -1282,9 +1279,6 @@
     <t>IPBES_GA_3_123_420; GEO_20_6_228</t>
   </si>
   <si>
-    <t>Variable vs composite index</t>
-  </si>
-  <si>
     <t>air quality index</t>
   </si>
   <si>
@@ -1300,9 +1294,6 @@
     <t>SDG_G3.5.2_40</t>
   </si>
   <si>
-    <t>Same concept; SDG 3.5.2 gives the formal definition</t>
-  </si>
-  <si>
     <t>alcohol use</t>
   </si>
   <si>
@@ -1786,9 +1777,6 @@
     <t>SDG_G7.3.1_97; IPBES_SUA_sup_7.3.1_41</t>
   </si>
   <si>
-    <t>Same concept; one with formal definition</t>
-  </si>
-  <si>
     <t>energy-intensity</t>
   </si>
   <si>
@@ -1900,9 +1888,6 @@
     <t>IPCC_sup_47</t>
   </si>
   <si>
-    <t>Index vs variable</t>
-  </si>
-  <si>
     <t>floods</t>
   </si>
   <si>
@@ -2821,9 +2806,6 @@
     <t>IPBES_GA_3_123_420</t>
   </si>
   <si>
-    <t>Variable vs index</t>
-  </si>
-  <si>
     <t>water quality index (watqi)</t>
   </si>
   <si>
@@ -2876,13 +2858,19 @@
   </si>
   <si>
     <t>Limitation: lexical matching misses synonyms with no shared words; groups are a review aid, not a final classification.</t>
+  </si>
+  <si>
+    <t>Concept vs indicator or index</t>
+  </si>
+  <si>
+    <t>Variable vs indicators or index</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2914,6 +2902,24 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2948,7 +2954,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2968,11 +2974,40 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -3233,21 +3268,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I346"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="8.453125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="42" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -3275,7 +3310,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -3302,7 +3337,7 @@
       </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -3329,7 +3364,7 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -3356,7 +3391,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
@@ -3383,7 +3418,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -3410,7 +3445,7 @@
       </c>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -3437,7 +3472,7 @@
       </c>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>36</v>
       </c>
@@ -3464,7 +3499,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
@@ -3491,7 +3526,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -3518,7 +3553,7 @@
       </c>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
@@ -3545,7 +3580,7 @@
       </c>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -3572,7 +3607,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>47</v>
       </c>
@@ -3599,7 +3634,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>47</v>
       </c>
@@ -3626,7 +3661,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>47</v>
       </c>
@@ -3653,7 +3688,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>47</v>
       </c>
@@ -3680,7 +3715,7 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>61</v>
       </c>
@@ -3707,7 +3742,7 @@
       </c>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>61</v>
       </c>
@@ -3734,7 +3769,7 @@
       </c>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>66</v>
       </c>
@@ -3761,7 +3796,7 @@
       </c>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -3788,7 +3823,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
@@ -3815,7 +3850,7 @@
       </c>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>72</v>
       </c>
@@ -3842,7 +3877,7 @@
       </c>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>72</v>
       </c>
@@ -3869,7 +3904,7 @@
       </c>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>78</v>
       </c>
@@ -3896,7 +3931,7 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>78</v>
       </c>
@@ -3923,7 +3958,7 @@
       </c>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>83</v>
       </c>
@@ -3950,7 +3985,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>83</v>
       </c>
@@ -3977,7 +4012,7 @@
       </c>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>89</v>
       </c>
@@ -4004,7 +4039,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>89</v>
       </c>
@@ -4031,7 +4066,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>95</v>
       </c>
@@ -4058,7 +4093,7 @@
       </c>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>95</v>
       </c>
@@ -4085,7 +4120,7 @@
       </c>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" s="8" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" s="8" customFormat="1" ht="50" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>99</v>
       </c>
@@ -4112,7 +4147,7 @@
       </c>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" spans="1:9" s="8" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" s="8" customFormat="1" ht="50" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>99</v>
       </c>
@@ -4139,7 +4174,7 @@
       </c>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>104</v>
       </c>
@@ -4166,7 +4201,7 @@
       </c>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>104</v>
       </c>
@@ -4193,7 +4228,7 @@
       </c>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>104</v>
       </c>
@@ -4220,7 +4255,7 @@
       </c>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>111</v>
       </c>
@@ -4247,7 +4282,7 @@
       </c>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>111</v>
       </c>
@@ -4274,7 +4309,7 @@
       </c>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -4301,7 +4336,7 @@
       </c>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>118</v>
       </c>
@@ -4328,7 +4363,7 @@
       </c>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>123</v>
       </c>
@@ -4355,7 +4390,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>123</v>
       </c>
@@ -4382,7 +4417,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>128</v>
       </c>
@@ -4409,7 +4444,7 @@
       </c>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>128</v>
       </c>
@@ -4436,7 +4471,7 @@
       </c>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>128</v>
       </c>
@@ -4463,7 +4498,7 @@
       </c>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>128</v>
       </c>
@@ -4490,7 +4525,7 @@
       </c>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>140</v>
       </c>
@@ -4517,7 +4552,7 @@
       </c>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>140</v>
       </c>
@@ -4544,7 +4579,7 @@
       </c>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>145</v>
       </c>
@@ -4571,7 +4606,7 @@
       </c>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>145</v>
       </c>
@@ -4598,7 +4633,7 @@
       </c>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>145</v>
       </c>
@@ -4625,7 +4660,7 @@
       </c>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>152</v>
       </c>
@@ -4652,7 +4687,7 @@
       </c>
       <c r="I52" s="3"/>
     </row>
-    <row r="53" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>152</v>
       </c>
@@ -4679,7 +4714,7 @@
       </c>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>156</v>
       </c>
@@ -4706,7 +4741,7 @@
       </c>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>156</v>
       </c>
@@ -4733,7 +4768,7 @@
       </c>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>161</v>
       </c>
@@ -4760,7 +4795,7 @@
       </c>
       <c r="I56" s="3"/>
     </row>
-    <row r="57" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>161</v>
       </c>
@@ -4787,7 +4822,7 @@
       </c>
       <c r="I57" s="3"/>
     </row>
-    <row r="58" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>166</v>
       </c>
@@ -4814,7 +4849,7 @@
       </c>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>166</v>
       </c>
@@ -4841,7 +4876,7 @@
       </c>
       <c r="I59" s="2"/>
     </row>
-    <row r="60" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>173</v>
       </c>
@@ -4868,7 +4903,7 @@
       </c>
       <c r="I60" s="3"/>
     </row>
-    <row r="61" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>173</v>
       </c>
@@ -4895,7 +4930,7 @@
       </c>
       <c r="I61" s="3"/>
     </row>
-    <row r="62" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>173</v>
       </c>
@@ -4922,7 +4957,7 @@
       </c>
       <c r="I62" s="3"/>
     </row>
-    <row r="63" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>183</v>
       </c>
@@ -4949,7 +4984,7 @@
       </c>
       <c r="I63" s="2"/>
     </row>
-    <row r="64" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>183</v>
       </c>
@@ -4976,7 +5011,7 @@
       </c>
       <c r="I64" s="2"/>
     </row>
-    <row r="65" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>188</v>
       </c>
@@ -5003,7 +5038,7 @@
       </c>
       <c r="I65" s="3"/>
     </row>
-    <row r="66" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>188</v>
       </c>
@@ -5030,7 +5065,7 @@
       </c>
       <c r="I66" s="3"/>
     </row>
-    <row r="67" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>192</v>
       </c>
@@ -5057,7 +5092,7 @@
       </c>
       <c r="I67" s="2"/>
     </row>
-    <row r="68" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>192</v>
       </c>
@@ -5084,7 +5119,7 @@
       </c>
       <c r="I68" s="2"/>
     </row>
-    <row r="69" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>197</v>
       </c>
@@ -5111,7 +5146,7 @@
       </c>
       <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>197</v>
       </c>
@@ -5138,7 +5173,7 @@
       </c>
       <c r="I70" s="3"/>
     </row>
-    <row r="71" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>202</v>
       </c>
@@ -5165,7 +5200,7 @@
       </c>
       <c r="I71" s="2"/>
     </row>
-    <row r="72" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>202</v>
       </c>
@@ -5192,7 +5227,7 @@
       </c>
       <c r="I72" s="2"/>
     </row>
-    <row r="73" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>207</v>
       </c>
@@ -5219,7 +5254,7 @@
       </c>
       <c r="I73" s="3"/>
     </row>
-    <row r="74" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>207</v>
       </c>
@@ -5246,7 +5281,7 @@
       </c>
       <c r="I74" s="3"/>
     </row>
-    <row r="75" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>211</v>
       </c>
@@ -5273,7 +5308,7 @@
       </c>
       <c r="I75" s="2"/>
     </row>
-    <row r="76" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>211</v>
       </c>
@@ -5300,7 +5335,7 @@
       </c>
       <c r="I76" s="2"/>
     </row>
-    <row r="77" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>217</v>
       </c>
@@ -5327,7 +5362,7 @@
       </c>
       <c r="I77" s="3"/>
     </row>
-    <row r="78" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>217</v>
       </c>
@@ -5354,7 +5389,7 @@
       </c>
       <c r="I78" s="3"/>
     </row>
-    <row r="79" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>222</v>
       </c>
@@ -5381,7 +5416,7 @@
       </c>
       <c r="I79" s="2"/>
     </row>
-    <row r="80" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>222</v>
       </c>
@@ -5408,7 +5443,7 @@
       </c>
       <c r="I80" s="2"/>
     </row>
-    <row r="81" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>222</v>
       </c>
@@ -5435,7 +5470,7 @@
       </c>
       <c r="I81" s="2"/>
     </row>
-    <row r="82" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>229</v>
       </c>
@@ -5462,7 +5497,7 @@
       </c>
       <c r="I82" s="3"/>
     </row>
-    <row r="83" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>229</v>
       </c>
@@ -5489,7 +5524,7 @@
       </c>
       <c r="I83" s="3"/>
     </row>
-    <row r="84" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>234</v>
       </c>
@@ -5516,7 +5551,7 @@
       </c>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>234</v>
       </c>
@@ -5543,7 +5578,7 @@
       </c>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>239</v>
       </c>
@@ -5570,7 +5605,7 @@
       </c>
       <c r="I86" s="3"/>
     </row>
-    <row r="87" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>239</v>
       </c>
@@ -5597,7 +5632,7 @@
       </c>
       <c r="I87" s="3"/>
     </row>
-    <row r="88" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>244</v>
       </c>
@@ -5624,7 +5659,7 @@
       </c>
       <c r="I88" s="2"/>
     </row>
-    <row r="89" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>244</v>
       </c>
@@ -5651,7 +5686,7 @@
       </c>
       <c r="I89" s="2"/>
     </row>
-    <row r="90" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>249</v>
       </c>
@@ -5678,7 +5713,7 @@
       </c>
       <c r="I90" s="3"/>
     </row>
-    <row r="91" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>249</v>
       </c>
@@ -5705,7 +5740,7 @@
       </c>
       <c r="I91" s="3"/>
     </row>
-    <row r="92" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>254</v>
       </c>
@@ -5732,7 +5767,7 @@
       </c>
       <c r="I92" s="2"/>
     </row>
-    <row r="93" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>254</v>
       </c>
@@ -5759,7 +5794,7 @@
       </c>
       <c r="I93" s="2"/>
     </row>
-    <row r="94" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>259</v>
       </c>
@@ -5786,7 +5821,7 @@
       </c>
       <c r="I94" s="3"/>
     </row>
-    <row r="95" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>259</v>
       </c>
@@ -5813,7 +5848,7 @@
       </c>
       <c r="I95" s="3"/>
     </row>
-    <row r="96" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>265</v>
       </c>
@@ -5840,7 +5875,7 @@
       </c>
       <c r="I96" s="2"/>
     </row>
-    <row r="97" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>265</v>
       </c>
@@ -5867,7 +5902,7 @@
       </c>
       <c r="I97" s="2"/>
     </row>
-    <row r="98" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>271</v>
       </c>
@@ -5894,7 +5929,7 @@
       </c>
       <c r="I98" s="3"/>
     </row>
-    <row r="99" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>271</v>
       </c>
@@ -5921,7 +5956,7 @@
       </c>
       <c r="I99" s="3"/>
     </row>
-    <row r="100" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>277</v>
       </c>
@@ -5948,7 +5983,7 @@
       </c>
       <c r="I100" s="2"/>
     </row>
-    <row r="101" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>277</v>
       </c>
@@ -5975,7 +6010,7 @@
       </c>
       <c r="I101" s="2"/>
     </row>
-    <row r="102" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>282</v>
       </c>
@@ -6002,7 +6037,7 @@
       </c>
       <c r="I102" s="3"/>
     </row>
-    <row r="103" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>282</v>
       </c>
@@ -6029,7 +6064,7 @@
       </c>
       <c r="I103" s="3"/>
     </row>
-    <row r="104" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>288</v>
       </c>
@@ -6056,7 +6091,7 @@
       </c>
       <c r="I104" s="2"/>
     </row>
-    <row r="105" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>288</v>
       </c>
@@ -6083,7 +6118,7 @@
       </c>
       <c r="I105" s="2"/>
     </row>
-    <row r="106" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>294</v>
       </c>
@@ -6110,7 +6145,7 @@
       </c>
       <c r="I106" s="3"/>
     </row>
-    <row r="107" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>294</v>
       </c>
@@ -6137,7 +6172,7 @@
       </c>
       <c r="I107" s="3"/>
     </row>
-    <row r="108" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>298</v>
       </c>
@@ -6164,7 +6199,7 @@
       </c>
       <c r="I108" s="2"/>
     </row>
-    <row r="109" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>298</v>
       </c>
@@ -6191,7 +6226,7 @@
       </c>
       <c r="I109" s="2"/>
     </row>
-    <row r="110" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>303</v>
       </c>
@@ -6218,7 +6253,7 @@
       </c>
       <c r="I110" s="3"/>
     </row>
-    <row r="111" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>303</v>
       </c>
@@ -6245,7 +6280,7 @@
       </c>
       <c r="I111" s="3"/>
     </row>
-    <row r="112" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>308</v>
       </c>
@@ -6272,7 +6307,7 @@
       </c>
       <c r="I112" s="2"/>
     </row>
-    <row r="113" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>308</v>
       </c>
@@ -6299,7 +6334,7 @@
       </c>
       <c r="I113" s="2"/>
     </row>
-    <row r="114" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>314</v>
       </c>
@@ -6326,7 +6361,7 @@
       </c>
       <c r="I114" s="3"/>
     </row>
-    <row r="115" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>314</v>
       </c>
@@ -6353,7 +6388,7 @@
       </c>
       <c r="I115" s="3"/>
     </row>
-    <row r="116" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>319</v>
       </c>
@@ -6380,7 +6415,7 @@
       </c>
       <c r="I116" s="2"/>
     </row>
-    <row r="117" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>319</v>
       </c>
@@ -6407,7 +6442,7 @@
       </c>
       <c r="I117" s="2"/>
     </row>
-    <row r="118" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>324</v>
       </c>
@@ -6434,7 +6469,7 @@
       </c>
       <c r="I118" s="3"/>
     </row>
-    <row r="119" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>324</v>
       </c>
@@ -6461,7 +6496,7 @@
       </c>
       <c r="I119" s="3"/>
     </row>
-    <row r="120" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>329</v>
       </c>
@@ -6488,7 +6523,7 @@
       </c>
       <c r="I120" s="2"/>
     </row>
-    <row r="121" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>329</v>
       </c>
@@ -6515,7 +6550,7 @@
       </c>
       <c r="I121" s="2"/>
     </row>
-    <row r="122" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>333</v>
       </c>
@@ -6542,7 +6577,7 @@
       </c>
       <c r="I122" s="3"/>
     </row>
-    <row r="123" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>333</v>
       </c>
@@ -6569,7 +6604,7 @@
       </c>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>339</v>
       </c>
@@ -6596,7 +6631,7 @@
       </c>
       <c r="I124" s="2"/>
     </row>
-    <row r="125" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>339</v>
       </c>
@@ -6623,7 +6658,7 @@
       </c>
       <c r="I125" s="2"/>
     </row>
-    <row r="126" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>344</v>
       </c>
@@ -6650,7 +6685,7 @@
       </c>
       <c r="I126" s="3"/>
     </row>
-    <row r="127" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>344</v>
       </c>
@@ -6677,7 +6712,7 @@
       </c>
       <c r="I127" s="3"/>
     </row>
-    <row r="128" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>349</v>
       </c>
@@ -6704,7 +6739,7 @@
       </c>
       <c r="I128" s="2"/>
     </row>
-    <row r="129" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>349</v>
       </c>
@@ -6731,7 +6766,7 @@
       </c>
       <c r="I129" s="2"/>
     </row>
-    <row r="130" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>353</v>
       </c>
@@ -6758,7 +6793,7 @@
       </c>
       <c r="I130" s="3"/>
     </row>
-    <row r="131" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>353</v>
       </c>
@@ -6785,7 +6820,7 @@
       </c>
       <c r="I131" s="3"/>
     </row>
-    <row r="132" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>358</v>
       </c>
@@ -6812,7 +6847,7 @@
       </c>
       <c r="I132" s="2"/>
     </row>
-    <row r="133" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>358</v>
       </c>
@@ -6839,7 +6874,7 @@
       </c>
       <c r="I133" s="2"/>
     </row>
-    <row r="134" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>363</v>
       </c>
@@ -6866,7 +6901,7 @@
       </c>
       <c r="I134" s="3"/>
     </row>
-    <row r="135" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>363</v>
       </c>
@@ -6893,7 +6928,7 @@
       </c>
       <c r="I135" s="3"/>
     </row>
-    <row r="136" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>369</v>
       </c>
@@ -6920,7 +6955,7 @@
       </c>
       <c r="I136" s="2"/>
     </row>
-    <row r="137" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>369</v>
       </c>
@@ -6947,7 +6982,7 @@
       </c>
       <c r="I137" s="2"/>
     </row>
-    <row r="138" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>374</v>
       </c>
@@ -6974,7 +7009,7 @@
       </c>
       <c r="I138" s="3"/>
     </row>
-    <row r="139" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>374</v>
       </c>
@@ -7001,7 +7036,7 @@
       </c>
       <c r="I139" s="3"/>
     </row>
-    <row r="140" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>380</v>
       </c>
@@ -7028,7 +7063,7 @@
       </c>
       <c r="I140" s="2"/>
     </row>
-    <row r="141" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>380</v>
       </c>
@@ -7055,7 +7090,7 @@
       </c>
       <c r="I141" s="2"/>
     </row>
-    <row r="142" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>384</v>
       </c>
@@ -7084,7 +7119,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>384</v>
       </c>
@@ -7113,7 +7148,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>391</v>
       </c>
@@ -7142,7 +7177,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>391</v>
       </c>
@@ -7171,14 +7206,14 @@
         <v>394</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>397</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="C146" s="7" t="s">
         <v>398</v>
       </c>
       <c r="D146" s="3" t="s">
@@ -7196,25 +7231,25 @@
       <c r="H146" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I146" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="I146" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>397</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>402</v>
+      <c r="C147" s="7" t="s">
+        <v>401</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>400</v>
@@ -7225,25 +7260,25 @@
       <c r="H147" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I147" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="I147" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>91</v>
@@ -7255,24 +7290,24 @@
         <v>24</v>
       </c>
       <c r="I148" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A149" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>407</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>91</v>
@@ -7284,24 +7319,24 @@
         <v>24</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C150" s="7" t="s">
         <v>410</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>366</v>
@@ -7312,25 +7347,25 @@
       <c r="H150" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I150" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I150" s="11" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C151" s="3" t="s">
-        <v>414</v>
+      <c r="C151" s="7" t="s">
+        <v>412</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>366</v>
@@ -7341,25 +7376,25 @@
       <c r="H151" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I151" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="I151" s="11" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>417</v>
+      <c r="C152" s="9" t="s">
+        <v>415</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>262</v>
@@ -7370,25 +7405,25 @@
       <c r="H152" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I152" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I152" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>420</v>
+      <c r="C153" s="9" t="s">
+        <v>417</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>262</v>
@@ -7399,25 +7434,25 @@
       <c r="H153" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I153" s="2" t="s">
+      <c r="I153" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A154" s="3" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="B154" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>170</v>
@@ -7429,24 +7464,24 @@
         <v>132</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>170</v>
@@ -7458,24 +7493,24 @@
         <v>132</v>
       </c>
       <c r="I155" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A156" s="2" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="B156" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>38</v>
@@ -7487,24 +7522,24 @@
         <v>27</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>38</v>
@@ -7516,24 +7551,24 @@
         <v>27</v>
       </c>
       <c r="I157" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A158" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>431</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A158" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>38</v>
@@ -7545,24 +7580,24 @@
         <v>27</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>38</v>
@@ -7574,24 +7609,24 @@
         <v>27</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>148</v>
@@ -7603,24 +7638,24 @@
         <v>27</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>148</v>
@@ -7632,24 +7667,24 @@
         <v>27</v>
       </c>
       <c r="I161" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A162" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C162" s="3" t="s">
         <v>440</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>148</v>
@@ -7661,24 +7696,24 @@
         <v>27</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>38</v>
@@ -7690,24 +7725,24 @@
         <v>24</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>38</v>
@@ -7719,24 +7754,24 @@
         <v>24</v>
       </c>
       <c r="I164" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A165" s="3" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
-        <v>451</v>
-      </c>
       <c r="B165" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C165" s="3" t="s">
-        <v>452</v>
+      <c r="C165" s="7" t="s">
+        <v>449</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>38</v>
@@ -7748,24 +7783,24 @@
         <v>27</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C166" s="3" t="s">
-        <v>455</v>
+      <c r="C166" s="7" t="s">
+        <v>452</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>38</v>
@@ -7777,24 +7812,24 @@
         <v>27</v>
       </c>
       <c r="I166" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A167" s="2" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
-        <v>457</v>
-      </c>
       <c r="B167" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>336</v>
@@ -7806,24 +7841,24 @@
         <v>35</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>336</v>
@@ -7835,24 +7870,24 @@
         <v>16</v>
       </c>
       <c r="I168" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A169" s="3" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
-        <v>463</v>
-      </c>
       <c r="B169" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C169" s="3" t="s">
-        <v>464</v>
+      <c r="C169" s="10" t="s">
+        <v>461</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>86</v>
@@ -7864,24 +7899,24 @@
         <v>27</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A170" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C170" s="3" t="s">
-        <v>467</v>
+      <c r="C170" s="10" t="s">
+        <v>464</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>86</v>
@@ -7893,24 +7928,24 @@
         <v>27</v>
       </c>
       <c r="I170" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A171" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C171" s="10" t="s">
         <v>466</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>86</v>
@@ -7922,24 +7957,24 @@
         <v>27</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A172" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>471</v>
+      <c r="C172" s="10" t="s">
+        <v>468</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>86</v>
@@ -7951,24 +7986,24 @@
         <v>24</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>38</v>
@@ -7980,24 +8015,24 @@
         <v>27</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>38</v>
@@ -8009,24 +8044,24 @@
         <v>27</v>
       </c>
       <c r="I174" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A175" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>475</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>38</v>
@@ -8038,18 +8073,18 @@
         <v>27</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>38</v>
@@ -8067,24 +8102,24 @@
         <v>27</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>274</v>
@@ -8096,24 +8131,24 @@
         <v>27</v>
       </c>
       <c r="I177" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A178" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E178" s="3" t="s">
         <v>484</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A178" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>274</v>
@@ -8125,24 +8160,24 @@
         <v>27</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>38</v>
@@ -8154,24 +8189,24 @@
         <v>27</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>38</v>
@@ -8183,24 +8218,24 @@
         <v>27</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>38</v>
@@ -8212,24 +8247,24 @@
         <v>27</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A182" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>50</v>
@@ -8241,24 +8276,24 @@
         <v>35</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>50</v>
@@ -8270,18 +8305,18 @@
         <v>35</v>
       </c>
       <c r="I183" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A184" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C184" s="3" t="s">
         <v>498</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A184" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>12</v>
@@ -8299,24 +8334,24 @@
         <v>35</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>50</v>
@@ -8328,24 +8363,24 @@
         <v>16</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>291</v>
@@ -8357,24 +8392,24 @@
         <v>132</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>291</v>
@@ -8386,24 +8421,24 @@
         <v>132</v>
       </c>
       <c r="I187" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A188" s="3" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A188" s="3" t="s">
-        <v>511</v>
-      </c>
       <c r="B188" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>170</v>
@@ -8415,24 +8450,24 @@
         <v>27</v>
       </c>
       <c r="I188" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>170</v>
@@ -8444,24 +8479,24 @@
         <v>27</v>
       </c>
       <c r="I189" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A190" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C190" s="3" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A190" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C190" s="3" t="s">
-        <v>517</v>
-      </c>
       <c r="D190" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>170</v>
@@ -8473,24 +8508,24 @@
         <v>27</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>170</v>
@@ -8502,24 +8537,24 @@
         <v>27</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C192" s="2" t="s">
-        <v>522</v>
+      <c r="C192" s="9" t="s">
+        <v>519</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>91</v>
@@ -8531,24 +8566,24 @@
         <v>27</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>525</v>
+      <c r="C193" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>91</v>
@@ -8560,24 +8595,24 @@
         <v>27</v>
       </c>
       <c r="I193" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A194" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C194" s="9" t="s">
         <v>524</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A194" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>527</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>91</v>
@@ -8589,24 +8624,24 @@
         <v>27</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>50</v>
@@ -8618,24 +8653,24 @@
         <v>27</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>50</v>
@@ -8647,24 +8682,24 @@
         <v>27</v>
       </c>
       <c r="I196" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A197" s="2" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A197" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="B197" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>86</v>
@@ -8676,24 +8711,24 @@
         <v>69</v>
       </c>
       <c r="I197" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>86</v>
@@ -8705,24 +8740,24 @@
         <v>69</v>
       </c>
       <c r="I198" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A199" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C199" s="2" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A199" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="D199" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>86</v>
@@ -8734,18 +8769,18 @@
         <v>214</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>12</v>
@@ -8763,18 +8798,18 @@
         <v>87</v>
       </c>
       <c r="I200" s="3" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C201" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C201" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>12</v>
@@ -8792,24 +8827,24 @@
         <v>35</v>
       </c>
       <c r="I201" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A202" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E202" s="3" t="s">
         <v>545</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A202" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E202" s="3" t="s">
-        <v>548</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>12</v>
@@ -8821,18 +8856,18 @@
         <v>35</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>30</v>
@@ -8850,24 +8885,24 @@
         <v>24</v>
       </c>
       <c r="I203" s="2" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>269</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>267</v>
@@ -8879,24 +8914,24 @@
         <v>35</v>
       </c>
       <c r="I204" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A205" s="3" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A205" s="3" t="s">
-        <v>554</v>
-      </c>
       <c r="B205" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>30</v>
@@ -8908,24 +8943,24 @@
         <v>27</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>30</v>
@@ -8937,24 +8972,24 @@
         <v>24</v>
       </c>
       <c r="I206" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A207" s="2" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A207" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="B207" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>14</v>
@@ -8966,24 +9001,24 @@
         <v>132</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>14</v>
@@ -8995,24 +9030,24 @@
         <v>132</v>
       </c>
       <c r="I208" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A209" s="3" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A209" s="3" t="s">
-        <v>566</v>
-      </c>
       <c r="B209" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>14</v>
@@ -9024,24 +9059,24 @@
         <v>16</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>14</v>
@@ -9053,24 +9088,24 @@
         <v>16</v>
       </c>
       <c r="I210" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A211" s="2" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A211" s="2" t="s">
-        <v>572</v>
-      </c>
       <c r="B211" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>50</v>
@@ -9082,24 +9117,24 @@
         <v>16</v>
       </c>
       <c r="I211" s="2" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>50</v>
@@ -9111,24 +9146,24 @@
         <v>24</v>
       </c>
       <c r="I212" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A213" s="3" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="213" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A213" s="3" t="s">
-        <v>578</v>
-      </c>
       <c r="B213" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C213" s="3" t="s">
-        <v>579</v>
+      <c r="C213" s="7" t="s">
+        <v>576</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>50</v>
@@ -9139,25 +9174,25 @@
       <c r="H213" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I213" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I213" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C214" s="7" t="s">
         <v>578</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>582</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>50</v>
@@ -9168,25 +9203,25 @@
       <c r="H214" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I214" s="3" t="s">
+      <c r="I214" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A215" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>581</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A215" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>38</v>
@@ -9198,24 +9233,24 @@
         <v>27</v>
       </c>
       <c r="I215" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>38</v>
@@ -9227,27 +9262,27 @@
         <v>27</v>
       </c>
       <c r="I216" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A217" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C217" s="3" t="s">
         <v>587</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A217" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C217" s="3" t="s">
-        <v>591</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>15</v>
@@ -9256,27 +9291,27 @@
         <v>27</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C218" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B218" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>594</v>
-      </c>
       <c r="D218" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G218" s="3" t="s">
         <v>15</v>
@@ -9285,27 +9320,27 @@
         <v>27</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A219" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G219" s="3" t="s">
         <v>15</v>
@@ -9314,18 +9349,18 @@
         <v>27</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>12</v>
@@ -9343,24 +9378,24 @@
         <v>69</v>
       </c>
       <c r="I220" s="2" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E221" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>602</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>12</v>
@@ -9372,24 +9407,24 @@
         <v>214</v>
       </c>
       <c r="I221" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A222" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C222" s="7" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="222" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A222" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>604</v>
-      </c>
       <c r="D222" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>170</v>
@@ -9401,24 +9436,24 @@
         <v>87</v>
       </c>
       <c r="I222" s="3" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="150" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C223" s="7" t="s">
         <v>603</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>607</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>168</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>170</v>
@@ -9430,24 +9465,24 @@
         <v>69</v>
       </c>
       <c r="I223" s="3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A224" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C224" s="2" t="s">
         <v>606</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>131</v>
@@ -9459,24 +9494,24 @@
         <v>132</v>
       </c>
       <c r="I224" s="2" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C225" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>613</v>
-      </c>
       <c r="D225" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>131</v>
@@ -9488,24 +9523,24 @@
         <v>132</v>
       </c>
       <c r="I225" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A226" s="3" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A226" s="3" t="s">
-        <v>616</v>
-      </c>
       <c r="B226" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C226" s="3" t="s">
-        <v>617</v>
+      <c r="C226" s="7" t="s">
+        <v>613</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>86</v>
@@ -9516,25 +9551,25 @@
       <c r="H226" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I226" s="3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I226" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A227" s="3" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C227" s="3" t="s">
-        <v>620</v>
+      <c r="C227" s="7" t="s">
+        <v>615</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>86</v>
@@ -9545,28 +9580,28 @@
       <c r="H227" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I227" s="3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I227" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -9575,27 +9610,27 @@
         <v>27</v>
       </c>
       <c r="I228" s="2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -9604,27 +9639,27 @@
         <v>27</v>
       </c>
       <c r="I229" s="2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -9633,18 +9668,18 @@
         <v>27</v>
       </c>
       <c r="I230" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A231" s="3" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="231" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A231" s="3" t="s">
-        <v>629</v>
-      </c>
       <c r="B231" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>12</v>
@@ -9662,24 +9697,24 @@
         <v>214</v>
       </c>
       <c r="I231" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>168</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>170</v>
@@ -9691,18 +9726,18 @@
         <v>214</v>
       </c>
       <c r="I232" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>38</v>
@@ -9720,24 +9755,24 @@
         <v>27</v>
       </c>
       <c r="I233" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>38</v>
@@ -9749,24 +9784,24 @@
         <v>27</v>
       </c>
       <c r="I234" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>38</v>
@@ -9778,24 +9813,24 @@
         <v>27</v>
       </c>
       <c r="I235" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A236" s="3" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A236" s="3" t="s">
-        <v>641</v>
-      </c>
       <c r="B236" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C236" s="3" t="s">
-        <v>642</v>
+      <c r="C236" s="10" t="s">
+        <v>637</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>148</v>
@@ -9807,24 +9842,24 @@
         <v>27</v>
       </c>
       <c r="I236" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C237" s="3" t="s">
-        <v>645</v>
+      <c r="C237" s="10" t="s">
+        <v>640</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>148</v>
@@ -9836,24 +9871,24 @@
         <v>27</v>
       </c>
       <c r="I237" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C238" s="10" t="s">
         <v>641</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C238" s="3" t="s">
-        <v>646</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>148</v>
@@ -9865,24 +9900,24 @@
         <v>27</v>
       </c>
       <c r="I238" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C239" s="3" t="s">
-        <v>648</v>
+      <c r="C239" s="10" t="s">
+        <v>643</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>284</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>148</v>
@@ -9894,24 +9929,24 @@
         <v>27</v>
       </c>
       <c r="I239" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C240" s="3" t="s">
-        <v>650</v>
+      <c r="C240" s="10" t="s">
+        <v>645</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>148</v>
@@ -9923,24 +9958,24 @@
         <v>27</v>
       </c>
       <c r="I240" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C241" s="3" t="s">
-        <v>652</v>
+      <c r="C241" s="10" t="s">
+        <v>647</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>148</v>
@@ -9952,24 +9987,24 @@
         <v>24</v>
       </c>
       <c r="I241" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>170</v>
@@ -9981,24 +10016,24 @@
         <v>69</v>
       </c>
       <c r="I242" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>170</v>
@@ -10010,24 +10045,24 @@
         <v>27</v>
       </c>
       <c r="I243" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A244" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E244" s="3" t="s">
         <v>657</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A244" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C244" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>662</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
@@ -10039,24 +10074,24 @@
         <v>132</v>
       </c>
       <c r="I244" s="3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E245" s="3" t="s">
         <v>660</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E245" s="3" t="s">
-        <v>665</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
@@ -10068,24 +10103,24 @@
         <v>132</v>
       </c>
       <c r="I245" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="150" x14ac:dyDescent="0.35">
+      <c r="A246" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>663</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A246" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>12</v>
@@ -10097,24 +10132,24 @@
         <v>35</v>
       </c>
       <c r="I246" s="2" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>12</v>
@@ -10126,24 +10161,24 @@
         <v>35</v>
       </c>
       <c r="I247" s="2" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>170</v>
@@ -10155,24 +10190,24 @@
         <v>69</v>
       </c>
       <c r="I248" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A249" s="3" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>168</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>170</v>
@@ -10184,24 +10219,24 @@
         <v>69</v>
       </c>
       <c r="I249" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>170</v>
@@ -10213,24 +10248,24 @@
         <v>27</v>
       </c>
       <c r="I250" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A251" s="2" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="251" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A251" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="B251" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>274</v>
@@ -10242,24 +10277,24 @@
         <v>132</v>
       </c>
       <c r="I251" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>274</v>
@@ -10271,24 +10306,24 @@
         <v>132</v>
       </c>
       <c r="I252" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>274</v>
@@ -10300,24 +10335,24 @@
         <v>132</v>
       </c>
       <c r="I253" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>274</v>
@@ -10329,24 +10364,24 @@
         <v>132</v>
       </c>
       <c r="I254" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>274</v>
@@ -10358,24 +10393,24 @@
         <v>87</v>
       </c>
       <c r="I255" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>274</v>
@@ -10387,24 +10422,24 @@
         <v>132</v>
       </c>
       <c r="I256" s="3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>274</v>
@@ -10416,24 +10451,24 @@
         <v>132</v>
       </c>
       <c r="I257" s="3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A258" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>694</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A258" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>170</v>
@@ -10445,24 +10480,24 @@
         <v>24</v>
       </c>
       <c r="I258" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>170</v>
@@ -10474,24 +10509,24 @@
         <v>24</v>
       </c>
       <c r="I259" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>170</v>
@@ -10503,24 +10538,24 @@
         <v>24</v>
       </c>
       <c r="I260" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A261" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C261" s="2" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="261" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A261" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>705</v>
-      </c>
       <c r="D261" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>170</v>
@@ -10532,24 +10567,24 @@
         <v>24</v>
       </c>
       <c r="I261" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>32</v>
@@ -10561,24 +10596,24 @@
         <v>24</v>
       </c>
       <c r="I262" s="3" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A263" s="3" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>32</v>
@@ -10590,24 +10625,24 @@
         <v>24</v>
       </c>
       <c r="I263" s="3" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>32</v>
@@ -10619,24 +10654,24 @@
         <v>24</v>
       </c>
       <c r="I264" s="3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A265" s="2" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A265" s="2" t="s">
-        <v>715</v>
-      </c>
       <c r="B265" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>32</v>
@@ -10648,18 +10683,18 @@
         <v>16</v>
       </c>
       <c r="I265" s="2" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>12</v>
@@ -10677,24 +10712,24 @@
         <v>35</v>
       </c>
       <c r="I266" s="2" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>38</v>
@@ -10706,24 +10741,24 @@
         <v>27</v>
       </c>
       <c r="I267" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>38</v>
@@ -10735,24 +10770,24 @@
         <v>27</v>
       </c>
       <c r="I268" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C269" s="2" t="s">
-        <v>727</v>
+      <c r="C269" s="9" t="s">
+        <v>722</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>170</v>
@@ -10764,24 +10799,24 @@
         <v>87</v>
       </c>
       <c r="I269" s="2" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="75" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>170</v>
@@ -10793,24 +10828,24 @@
         <v>87</v>
       </c>
       <c r="I270" s="2" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A271" s="3" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>274</v>
@@ -10822,24 +10857,24 @@
         <v>16</v>
       </c>
       <c r="I271" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E272" s="3" t="s">
-        <v>737</v>
+      <c r="E272" s="11" t="s">
+        <v>732</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>274</v>
@@ -10851,24 +10886,24 @@
         <v>24</v>
       </c>
       <c r="I272" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>86</v>
@@ -10880,18 +10915,18 @@
         <v>27</v>
       </c>
       <c r="I273" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>12</v>
@@ -10909,24 +10944,24 @@
         <v>27</v>
       </c>
       <c r="I274" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="D275" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>336</v>
@@ -10938,24 +10973,24 @@
         <v>132</v>
       </c>
       <c r="I275" s="3" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>336</v>
@@ -10967,24 +11002,24 @@
         <v>16</v>
       </c>
       <c r="I276" s="3" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>274</v>
@@ -10996,24 +11031,24 @@
         <v>69</v>
       </c>
       <c r="I277" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>274</v>
@@ -11025,24 +11060,24 @@
         <v>69</v>
       </c>
       <c r="I278" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>274</v>
@@ -11054,24 +11089,24 @@
         <v>69</v>
       </c>
       <c r="I279" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+      <c r="A280" s="3" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="280" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A280" s="3" t="s">
-        <v>757</v>
-      </c>
       <c r="B280" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C280" s="3" t="s">
-        <v>758</v>
+      <c r="C280" s="7" t="s">
+        <v>753</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>176</v>
@@ -11083,24 +11118,24 @@
         <v>214</v>
       </c>
       <c r="I280" s="3" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E281" s="3" t="s">
         <v>757</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C281" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E281" s="3" t="s">
-        <v>762</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>176</v>
@@ -11112,24 +11147,24 @@
         <v>132</v>
       </c>
       <c r="I281" s="3" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>355</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>176</v>
@@ -11141,24 +11176,24 @@
         <v>132</v>
       </c>
       <c r="I282" s="3" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A283" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C283" s="3" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="283" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A283" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C283" s="3" t="s">
-        <v>765</v>
-      </c>
       <c r="D283" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>176</v>
@@ -11170,24 +11205,24 @@
         <v>24</v>
       </c>
       <c r="I283" s="3" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>12</v>
@@ -11199,24 +11234,24 @@
         <v>132</v>
       </c>
       <c r="I284" s="2" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E285" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>12</v>
@@ -11228,24 +11263,24 @@
         <v>132</v>
       </c>
       <c r="I285" s="2" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="D286" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>274</v>
@@ -11257,24 +11292,24 @@
         <v>35</v>
       </c>
       <c r="I286" s="3" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E287" s="3" t="s">
         <v>773</v>
-      </c>
-      <c r="B287" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C287" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="D287" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="E287" s="3" t="s">
-        <v>778</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>274</v>
@@ -11286,24 +11321,24 @@
         <v>35</v>
       </c>
       <c r="I287" s="3" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>170</v>
@@ -11315,24 +11350,24 @@
         <v>132</v>
       </c>
       <c r="I288" s="2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>170</v>
@@ -11344,18 +11379,18 @@
         <v>132</v>
       </c>
       <c r="I289" s="2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>12</v>
@@ -11373,18 +11408,18 @@
         <v>132</v>
       </c>
       <c r="I290" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A291" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C291" s="3" t="s">
         <v>782</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A291" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="B291" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C291" s="3" t="s">
-        <v>787</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>12</v>
@@ -11402,24 +11437,24 @@
         <v>132</v>
       </c>
       <c r="I291" s="3" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
@@ -11431,24 +11466,24 @@
         <v>132</v>
       </c>
       <c r="I292" s="3" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A293" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E293" s="2" t="s">
         <v>788</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A293" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="D293" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>14</v>
@@ -11460,24 +11495,24 @@
         <v>35</v>
       </c>
       <c r="I293" s="2" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>14</v>
@@ -11489,24 +11524,24 @@
         <v>35</v>
       </c>
       <c r="I294" s="2" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="D295" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
@@ -11518,18 +11553,18 @@
         <v>132</v>
       </c>
       <c r="I295" s="3" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>12</v>
@@ -11547,24 +11582,24 @@
         <v>132</v>
       </c>
       <c r="I296" s="3" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>274</v>
@@ -11576,24 +11611,24 @@
         <v>35</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>274</v>
@@ -11605,24 +11640,24 @@
         <v>35</v>
       </c>
       <c r="I298" s="2" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>168</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>170</v>
@@ -11634,18 +11669,18 @@
         <v>24</v>
       </c>
       <c r="I299" s="3" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>12</v>
@@ -11663,24 +11698,24 @@
         <v>24</v>
       </c>
       <c r="I300" s="3" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>291</v>
@@ -11692,24 +11727,24 @@
         <v>132</v>
       </c>
       <c r="I301" s="2" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E302" s="2" t="s">
-        <v>816</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>291</v>
@@ -11721,24 +11756,24 @@
         <v>132</v>
       </c>
       <c r="I302" s="2" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="D303" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>91</v>
@@ -11750,24 +11785,24 @@
         <v>69</v>
       </c>
       <c r="I303" s="3" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="D304" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>91</v>
@@ -11779,24 +11814,24 @@
         <v>132</v>
       </c>
       <c r="I304" s="3" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A305" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>820</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A305" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="D305" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E305" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>170</v>
@@ -11808,24 +11843,24 @@
         <v>27</v>
       </c>
       <c r="I305" s="2" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C306" s="2" t="s">
-        <v>827</v>
+      <c r="C306" s="9" t="s">
+        <v>822</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>170</v>
@@ -11837,24 +11872,24 @@
         <v>27</v>
       </c>
       <c r="I306" s="2" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>170</v>
@@ -11866,24 +11901,24 @@
         <v>27</v>
       </c>
       <c r="I307" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A308" s="3" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="308" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A308" s="3" t="s">
-        <v>831</v>
-      </c>
       <c r="B308" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="D308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
@@ -11895,24 +11930,24 @@
         <v>214</v>
       </c>
       <c r="I308" s="3" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E309" s="3" t="s">
         <v>831</v>
-      </c>
-      <c r="B309" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C309" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="D309" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E309" s="3" t="s">
-        <v>836</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
@@ -11924,24 +11959,24 @@
         <v>214</v>
       </c>
       <c r="I309" s="3" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>310</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>310</v>
@@ -11953,24 +11988,24 @@
         <v>132</v>
       </c>
       <c r="I310" s="2" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>310</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>310</v>
@@ -11982,24 +12017,24 @@
         <v>27</v>
       </c>
       <c r="I311" s="2" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="D312" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>366</v>
@@ -12011,18 +12046,18 @@
         <v>24</v>
       </c>
       <c r="I312" s="3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="D313" s="3" t="s">
         <v>12</v>
@@ -12040,24 +12075,24 @@
         <v>24</v>
       </c>
       <c r="I313" s="3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>38</v>
@@ -12069,24 +12104,24 @@
         <v>27</v>
       </c>
       <c r="I314" s="2" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>38</v>
@@ -12098,18 +12133,18 @@
         <v>27</v>
       </c>
       <c r="I315" s="2" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="D316" s="3" t="s">
         <v>12</v>
@@ -12127,24 +12162,24 @@
         <v>69</v>
       </c>
       <c r="I316" s="3" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D317" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>32</v>
@@ -12156,24 +12191,24 @@
         <v>69</v>
       </c>
       <c r="I317" s="3" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A318" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>854</v>
-      </c>
-    </row>
-    <row r="318" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A318" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C318" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="D318" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>859</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>170</v>
@@ -12185,24 +12220,24 @@
         <v>24</v>
       </c>
       <c r="I318" s="2" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>170</v>
@@ -12214,24 +12249,24 @@
         <v>24</v>
       </c>
       <c r="I319" s="2" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>170</v>
@@ -12243,18 +12278,18 @@
         <v>24</v>
       </c>
       <c r="I320" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A321" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C321" s="2" t="s">
         <v>860</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A321" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C321" s="2" t="s">
-        <v>865</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>12</v>
@@ -12272,24 +12307,24 @@
         <v>24</v>
       </c>
       <c r="I321" s="2" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>14</v>
@@ -12301,24 +12336,24 @@
         <v>214</v>
       </c>
       <c r="I322" s="3" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C323" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E323" s="3" t="s">
         <v>866</v>
-      </c>
-      <c r="B323" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C323" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="D323" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E323" s="3" t="s">
-        <v>871</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>14</v>
@@ -12330,18 +12365,18 @@
         <v>214</v>
       </c>
       <c r="I323" s="3" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>12</v>
@@ -12359,24 +12394,24 @@
         <v>214</v>
       </c>
       <c r="I324" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A325" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C325" s="2" t="s">
         <v>869</v>
       </c>
-    </row>
-    <row r="325" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A325" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>874</v>
-      </c>
       <c r="D325" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>12</v>
@@ -12388,24 +12423,24 @@
         <v>214</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="D326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
@@ -12417,18 +12452,18 @@
         <v>87</v>
       </c>
       <c r="I326" s="3" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="D327" s="3" t="s">
         <v>12</v>
@@ -12446,24 +12481,24 @@
         <v>87</v>
       </c>
       <c r="I327" s="3" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>38</v>
@@ -12475,24 +12510,24 @@
         <v>27</v>
       </c>
       <c r="I328" s="2" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>38</v>
@@ -12504,24 +12539,24 @@
         <v>27</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>38</v>
@@ -12533,18 +12568,18 @@
         <v>27</v>
       </c>
       <c r="I330" s="3" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A331" s="3" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="D331" s="3" t="s">
         <v>38</v>
@@ -12562,24 +12597,24 @@
         <v>27</v>
       </c>
       <c r="I331" s="3" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="332" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>170</v>
@@ -12591,24 +12626,24 @@
         <v>214</v>
       </c>
       <c r="I332" s="2" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="333" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>170</v>
@@ -12620,24 +12655,24 @@
         <v>214</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
@@ -12649,24 +12684,24 @@
         <v>24</v>
       </c>
       <c r="I334" s="3" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="335" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
@@ -12678,18 +12713,18 @@
         <v>24</v>
       </c>
       <c r="I335" s="3" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>12</v>
@@ -12707,24 +12742,24 @@
         <v>69</v>
       </c>
       <c r="I336" s="2" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="F337" s="2" t="s">
         <v>12</v>
@@ -12736,27 +12771,27 @@
         <v>69</v>
       </c>
       <c r="I337" s="2" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="338" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C338" s="3" t="s">
-        <v>905</v>
+      <c r="C338" s="7" t="s">
+        <v>900</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="F338" s="3" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="G338" s="3" t="s">
         <v>15</v>
@@ -12765,27 +12800,27 @@
         <v>16</v>
       </c>
       <c r="I338" s="3" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="339" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C339" s="7" t="s">
         <v>904</v>
-      </c>
-      <c r="B339" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C339" s="3" t="s">
-        <v>909</v>
       </c>
       <c r="D339" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="G339" s="3" t="s">
         <v>15</v>
@@ -12794,27 +12829,27 @@
         <v>16</v>
       </c>
       <c r="I339" s="3" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="340" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C340" s="3" t="s">
-        <v>911</v>
+      <c r="C340" s="7" t="s">
+        <v>906</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="G340" s="3" t="s">
         <v>15</v>
@@ -12823,24 +12858,24 @@
         <v>132</v>
       </c>
       <c r="I340" s="3" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A341" s="2" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="341" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A341" s="2" t="s">
-        <v>913</v>
-      </c>
       <c r="B341" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>12</v>
@@ -12852,24 +12887,24 @@
         <v>24</v>
       </c>
       <c r="I341" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>12</v>
@@ -12881,24 +12916,24 @@
         <v>24</v>
       </c>
       <c r="I342" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>38</v>
@@ -12910,24 +12945,24 @@
         <v>24</v>
       </c>
       <c r="I343" s="3" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A344" s="3" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>385</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>38</v>
@@ -12939,24 +12974,24 @@
         <v>24</v>
       </c>
       <c r="I344" s="3" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A345" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C345" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E345" s="2" t="s">
         <v>920</v>
-      </c>
-    </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A345" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C345" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="D345" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E345" s="2" t="s">
-        <v>925</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>12</v>
@@ -12967,25 +13002,25 @@
       <c r="H345" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I345" s="2" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I345" s="11" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C346" s="2" t="s">
-        <v>927</v>
+      <c r="C346" s="9" t="s">
+        <v>921</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>12</v>
@@ -12996,12 +13031,12 @@
       <c r="H346" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I346" s="2" t="s">
-        <v>926</v>
+      <c r="I346" s="11" t="s">
+        <v>940</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I346" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I346" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -13010,68 +13045,68 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="B2" s="5">
         <f>SUMPRODUCT(('Similar indicators'!B2:B346="Same metric, different wording")/COUNTIF('Similar indicators'!A2:A346,'Similar indicators'!A2:A346))</f>
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="B3" s="5">
         <f>SUMPRODUCT(('Similar indicators'!B2:B346="Near-equivalent")/COUNTIF('Similar indicators'!A2:A346,'Similar indicators'!A2:A346))</f>
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Similar indicators'!B2:B346,"Same metric, different wording")</f>
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Similar indicators'!B2:B346,"Near-equivalent")</f>
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="B6" s="5">
         <f>SUMPRODUCT(('Similar indicators'!B2:B346="Same metric, different wording")*('Similar indicators'!G2:G346="Yes")/COUNTIF('Similar indicators'!A2:A346,'Similar indicators'!A2:A346))</f>
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="B7" s="5">
         <f>SUMPRODUCT(('Similar indicators'!G2:G346="Yes")/COUNTIF('Similar indicators'!A2:A346,'Similar indicators'!A2:A346))</f>
@@ -13087,49 +13122,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
         <v>938</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="27" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="27" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>944</v>
       </c>
     </row>
   </sheetData>
